--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_apoyopot_a_2018_la_araucania.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:47</t>
+    <t xml:space="preserve">2026-09-24 00:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
